--- a/docs/agile/test-cases/AgentMesh_Sprint1_TestCases.xlsx
+++ b/docs/agile/test-cases/AgentMesh_Sprint1_TestCases.xlsx
@@ -1720,7 +1720,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>All 23 test cases passed in CI on 2026-10-18: https://github.com/Soumen2581/Capstone-Project/actions/runs/39189608664</t>
+          <t>All 23 test cases passed in CI on 2026-10-18. CI workflow: https://github.com/htmw/F2026-T2-Phoenix/actions/workflows/ci.yml</t>
         </is>
       </c>
     </row>

--- a/docs/agile/test-cases/AgentMesh_Sprint1_TestCases.xlsx
+++ b/docs/agile/test-cases/AgentMesh_Sprint1_TestCases.xlsx
@@ -1720,7 +1720,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>All 23 test cases passed in CI on 2026-10-18. CI workflow: https://github.com/htmw/F2026-T2-Phoenix/actions/workflows/ci.yml</t>
+          <t>All 23 test cases passed in CI on 2026-10-18: https://github.com/Soumen2581/Capstone-Project/actions/runs/39189608664</t>
         </is>
       </c>
     </row>
